--- a/cloudflare-deploy/public/library/student/student-en.xlsx
+++ b/cloudflare-deploy/public/library/student/student-en.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2596,6 +2596,60 @@
       <c r="E53" s="20" t="inlineStr">
         <is>
           <t>Avoid days with school commitments. Choosing well up front beats rescheduling later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="54" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>🌊</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>Rescue Voyage (Mango Rescue Voyage)</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>Open 🌊 Rescue Voyage in the games hub. → Pick English / 中文 mode and press Start. → Steer your boat to the word friends in the water and lift them out. → Avoid the sharks, turtles and dolphins. → When rescue ends, take on the repeat-the-sentence mission.</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>The sentence mission from your rescued words is the real review — repeat it aloud, clearly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="54" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>🌟</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>[Parents] Pentagon Monthly Report</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>Open the report link you received on KakaoTalk. → Check the balance of the five strengths in the pentagon graph at the top. → Read This Period's Status (attendance, judgment) and the Teacher's Note. → Note the How You Can Help at Home tips. → To keep a paper copy, press 🖨 Print/PDF at the top.</t>
+        </is>
+      </c>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>An evenly large pentagon means balanced learning. A dented axis is this month's challenge.</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F588"/>
+  <dimension ref="A1:F616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9143,8 +9197,324 @@
       <c r="E588" s="33" t="n"/>
       <c r="F588" s="33" t="n"/>
     </row>
+    <row r="590" ht="26" customHeight="1">
+      <c r="A590" s="21" t="inlineStr">
+        <is>
+          <t>51  🌊 Rescue Voyage (Mango Rescue Voyage)  —  Rescue sea friends while you learn words</t>
+        </is>
+      </c>
+      <c r="B590" s="22" t="n"/>
+      <c r="C590" s="22" t="n"/>
+      <c r="D590" s="22" t="n"/>
+      <c r="E590" s="22" t="n"/>
+      <c r="F590" s="22" t="n"/>
+    </row>
+    <row r="591" ht="42" customHeight="1">
+      <c r="A591" s="23" t="inlineStr">
+        <is>
+          <t>📖 Swept up by a storm, word friends have fallen into the sea — steer your boat and lift them out. Rescue one and its native pronunciation and meaning are revealed; along the way, dodge sea creatures like sharks, turtles and dolphins. After rescuing as many as you can in time, a listen-and-repeat sentence mission follows, built from the words you saved.</t>
+        </is>
+      </c>
+      <c r="B591" s="24" t="n"/>
+      <c r="C591" s="24" t="n"/>
+      <c r="D591" s="24" t="n"/>
+      <c r="E591" s="24" t="n"/>
+      <c r="F591" s="24" t="n"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B592" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="593" ht="30" customHeight="1">
+      <c r="A593" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B593" s="28" t="inlineStr">
+        <is>
+          <t>Open 🌊 Rescue Voyage in the games hub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594" ht="30" customHeight="1">
+      <c r="A594" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B594" s="28" t="inlineStr">
+        <is>
+          <t>Pick English / 中文 mode and press Start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595" ht="30" customHeight="1">
+      <c r="A595" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B595" s="28" t="inlineStr">
+        <is>
+          <t>Steer your boat to the word friends in the water and lift them out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596" ht="30" customHeight="1">
+      <c r="A596" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B596" s="28" t="inlineStr">
+        <is>
+          <t>Avoid the sharks, turtles and dolphins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597" ht="30" customHeight="1">
+      <c r="A597" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B597" s="28" t="inlineStr">
+        <is>
+          <t>When rescue ends, take on the repeat-the-sentence mission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598" ht="24" customHeight="1">
+      <c r="A598" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B598" s="30" t="inlineStr">
+        <is>
+          <t>Each rescue plays the native pronunciation, so it's listening practice too.</t>
+        </is>
+      </c>
+      <c r="C598" s="31" t="n"/>
+      <c r="D598" s="31" t="n"/>
+      <c r="E598" s="31" t="n"/>
+      <c r="F598" s="31" t="n"/>
+    </row>
+    <row r="599" ht="24" customHeight="1">
+      <c r="A599" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B599" s="30" t="inlineStr">
+        <is>
+          <t>English and Chinese modes play the same way.</t>
+        </is>
+      </c>
+      <c r="C599" s="31" t="n"/>
+      <c r="D599" s="31" t="n"/>
+      <c r="E599" s="31" t="n"/>
+      <c r="F599" s="31" t="n"/>
+    </row>
+    <row r="600" ht="24" customHeight="1">
+      <c r="A600" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B600" s="30" t="inlineStr">
+        <is>
+          <t>Lifelike sea creatures make it more immersive.</t>
+        </is>
+      </c>
+      <c r="C600" s="31" t="n"/>
+      <c r="D600" s="31" t="n"/>
+      <c r="E600" s="31" t="n"/>
+      <c r="F600" s="31" t="n"/>
+    </row>
+    <row r="601" ht="26" customHeight="1">
+      <c r="A601" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · This game is motion-heavy. On a slower device, take a short break if it lags.</t>
+        </is>
+      </c>
+      <c r="B601" s="35" t="n"/>
+      <c r="C601" s="35" t="n"/>
+      <c r="D601" s="35" t="n"/>
+      <c r="E601" s="35" t="n"/>
+      <c r="F601" s="35" t="n"/>
+    </row>
+    <row r="602" ht="30" customHeight="1">
+      <c r="A602" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · The sentence mission from your rescued words is the real review — repeat it aloud, clearly.</t>
+        </is>
+      </c>
+      <c r="B602" s="33" t="n"/>
+      <c r="C602" s="33" t="n"/>
+      <c r="D602" s="33" t="n"/>
+      <c r="E602" s="33" t="n"/>
+      <c r="F602" s="33" t="n"/>
+    </row>
+    <row r="604" ht="26" customHeight="1">
+      <c r="A604" s="21" t="inlineStr">
+        <is>
+          <t>52  🌟 [Parents] Pentagon Monthly Report  —  Five strengths at a glance · print in one tap</t>
+        </is>
+      </c>
+      <c r="B604" s="22" t="n"/>
+      <c r="C604" s="22" t="n"/>
+      <c r="D604" s="22" t="n"/>
+      <c r="E604" s="22" t="n"/>
+      <c r="F604" s="22" t="n"/>
+    </row>
+    <row r="605" ht="42" customHeight="1">
+      <c r="A605" s="23" t="inlineStr">
+        <is>
+          <t>📖 A report card that shows your child's month across five axes of a pentagon graph — Pronunciation &amp; Fluency / Vocabulary / Sentence Building / Class Attitude / Participation — followed by attendance, judgment index and a teacher's note. The Print/PDF button up top outputs it as-is or saves a file.</t>
+        </is>
+      </c>
+      <c r="B605" s="24" t="n"/>
+      <c r="C605" s="24" t="n"/>
+      <c r="D605" s="24" t="n"/>
+      <c r="E605" s="24" t="n"/>
+      <c r="F605" s="24" t="n"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B606" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="607" ht="30" customHeight="1">
+      <c r="A607" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B607" s="28" t="inlineStr">
+        <is>
+          <t>Open the report link you received on KakaoTalk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608" ht="30" customHeight="1">
+      <c r="A608" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B608" s="28" t="inlineStr">
+        <is>
+          <t>Check the balance of the five strengths in the pentagon graph at the top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609" ht="30" customHeight="1">
+      <c r="A609" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B609" s="28" t="inlineStr">
+        <is>
+          <t>Read This Period's Status (attendance, judgment) and the Teacher's Note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610" ht="30" customHeight="1">
+      <c r="A610" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B610" s="28" t="inlineStr">
+        <is>
+          <t>Note the How You Can Help at Home tips.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611" ht="30" customHeight="1">
+      <c r="A611" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B611" s="28" t="inlineStr">
+        <is>
+          <t>To keep a paper copy, press 🖨 Print/PDF at the top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612" ht="24" customHeight="1">
+      <c r="A612" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B612" s="30" t="inlineStr">
+        <is>
+          <t>Only axes with real records are filled in — no invented numbers.</t>
+        </is>
+      </c>
+      <c r="C612" s="31" t="n"/>
+      <c r="D612" s="31" t="n"/>
+      <c r="E612" s="31" t="n"/>
+      <c r="F612" s="31" t="n"/>
+    </row>
+    <row r="613" ht="24" customHeight="1">
+      <c r="A613" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B613" s="30" t="inlineStr">
+        <is>
+          <t>Compiled every two months, so the trend is easy to read.</t>
+        </is>
+      </c>
+      <c r="C613" s="31" t="n"/>
+      <c r="D613" s="31" t="n"/>
+      <c r="E613" s="31" t="n"/>
+      <c r="F613" s="31" t="n"/>
+    </row>
+    <row r="614" ht="24" customHeight="1">
+      <c r="A614" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B614" s="30" t="inlineStr">
+        <is>
+          <t>It all fits one screen — a single printed page.</t>
+        </is>
+      </c>
+      <c r="C614" s="31" t="n"/>
+      <c r="D614" s="31" t="n"/>
+      <c r="E614" s="31" t="n"/>
+      <c r="F614" s="31" t="n"/>
+    </row>
+    <row r="615" ht="26" customHeight="1">
+      <c r="A615" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · The report fills in as learning records accumulate. In a low-activity month some axes may look empty.</t>
+        </is>
+      </c>
+      <c r="B615" s="35" t="n"/>
+      <c r="C615" s="35" t="n"/>
+      <c r="D615" s="35" t="n"/>
+      <c r="E615" s="35" t="n"/>
+      <c r="F615" s="35" t="n"/>
+    </row>
+    <row r="616" ht="30" customHeight="1">
+      <c r="A616" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · An evenly large pentagon means balanced learning. A dented axis is this month's challenge.</t>
+        </is>
+      </c>
+      <c r="B616" s="33" t="n"/>
+      <c r="C616" s="33" t="n"/>
+      <c r="D616" s="33" t="n"/>
+      <c r="E616" s="33" t="n"/>
+      <c r="F616" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="538">
+  <mergeCells count="564">
     <mergeCell ref="A183:F183"/>
     <mergeCell ref="B209:F209"/>
     <mergeCell ref="B445:F445"/>
@@ -9165,6 +9535,7 @@
     <mergeCell ref="A274:F274"/>
     <mergeCell ref="A372:F372"/>
     <mergeCell ref="B515:F515"/>
+    <mergeCell ref="A605:F605"/>
     <mergeCell ref="A107:F107"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A549:F549"/>
@@ -9200,6 +9571,7 @@
     <mergeCell ref="B446:F446"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A435:F435"/>
+    <mergeCell ref="B609:F609"/>
     <mergeCell ref="A362:F362"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B146:F146"/>
@@ -9232,6 +9604,7 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B249:F249"/>
     <mergeCell ref="A510:F510"/>
+    <mergeCell ref="B599:F599"/>
     <mergeCell ref="A295:F295"/>
     <mergeCell ref="A143:F143"/>
     <mergeCell ref="A334:F334"/>
@@ -9241,6 +9614,7 @@
     <mergeCell ref="B91:F91"/>
     <mergeCell ref="B327:F327"/>
     <mergeCell ref="B454:F454"/>
+    <mergeCell ref="B612:F612"/>
     <mergeCell ref="A365:F365"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B93:F93"/>
@@ -9273,6 +9647,7 @@
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B277:F277"/>
+    <mergeCell ref="B600:F600"/>
     <mergeCell ref="B404:F404"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="B81:F81"/>
@@ -9341,6 +9716,7 @@
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="A282:F282"/>
+    <mergeCell ref="B596:F596"/>
     <mergeCell ref="B571:F571"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A242:F242"/>
@@ -9388,11 +9764,14 @@
     <mergeCell ref="A96:F96"/>
     <mergeCell ref="B337:F337"/>
     <mergeCell ref="B579:F579"/>
+    <mergeCell ref="B610:F610"/>
+    <mergeCell ref="B597:F597"/>
     <mergeCell ref="B103:F103"/>
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="B205:F205"/>
     <mergeCell ref="B339:F339"/>
     <mergeCell ref="A352:F352"/>
+    <mergeCell ref="A615:F615"/>
     <mergeCell ref="B501:F501"/>
     <mergeCell ref="A485:F485"/>
     <mergeCell ref="B526:F526"/>
@@ -9413,12 +9792,14 @@
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B465:F465"/>
     <mergeCell ref="B350:F350"/>
+    <mergeCell ref="B592:F592"/>
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B431:F431"/>
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B287:F287"/>
     <mergeCell ref="B358:F358"/>
     <mergeCell ref="B529:F529"/>
+    <mergeCell ref="B594:F594"/>
     <mergeCell ref="A200:F200"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="A265:F265"/>
@@ -9432,6 +9813,7 @@
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B384:F384"/>
     <mergeCell ref="B378:F378"/>
+    <mergeCell ref="B607:F607"/>
     <mergeCell ref="A422:F422"/>
     <mergeCell ref="B144:F144"/>
     <mergeCell ref="B442:F442"/>
@@ -9455,12 +9837,15 @@
     <mergeCell ref="B520:F520"/>
     <mergeCell ref="B308:F308"/>
     <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B593:F593"/>
     <mergeCell ref="B397:F397"/>
     <mergeCell ref="B360:F360"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="A142:F142"/>
     <mergeCell ref="B239:F239"/>
     <mergeCell ref="B310:F310"/>
+    <mergeCell ref="B608:F608"/>
+    <mergeCell ref="B595:F595"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B361:F361"/>
@@ -9477,11 +9862,13 @@
     <mergeCell ref="A203:F203"/>
     <mergeCell ref="B542:F542"/>
     <mergeCell ref="B229:F229"/>
+    <mergeCell ref="B613:F613"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="A140:F140"/>
     <mergeCell ref="B514:F514"/>
     <mergeCell ref="B452:F452"/>
+    <mergeCell ref="B606:F606"/>
     <mergeCell ref="B544:F544"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="B258:F258"/>
@@ -9518,7 +9905,9 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B440:F440"/>
     <mergeCell ref="B240:F240"/>
+    <mergeCell ref="B611:F611"/>
     <mergeCell ref="A234:F234"/>
+    <mergeCell ref="B598:F598"/>
     <mergeCell ref="B377:F377"/>
     <mergeCell ref="A211:F211"/>
     <mergeCell ref="B329:F329"/>
@@ -9526,6 +9915,7 @@
     <mergeCell ref="A275:F275"/>
     <mergeCell ref="B316:F316"/>
     <mergeCell ref="B565:F565"/>
+    <mergeCell ref="B614:F614"/>
     <mergeCell ref="A511:F511"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B266:F266"/>
@@ -9552,7 +9942,10 @@
     <mergeCell ref="A587:F587"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A524:F524"/>
+    <mergeCell ref="A616:F616"/>
+    <mergeCell ref="A601:F601"/>
     <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A591:F591"/>
     <mergeCell ref="A224:F224"/>
     <mergeCell ref="A588:F588"/>
     <mergeCell ref="A72:F72"/>
@@ -9602,6 +9995,7 @@
     <mergeCell ref="B269:F269"/>
     <mergeCell ref="A403:F403"/>
     <mergeCell ref="B187:F187"/>
+    <mergeCell ref="A590:F590"/>
     <mergeCell ref="A182:F182"/>
     <mergeCell ref="A304:F304"/>
     <mergeCell ref="B556:F556"/>
@@ -9650,10 +10044,12 @@
     <mergeCell ref="B206:F206"/>
     <mergeCell ref="A233:F233"/>
     <mergeCell ref="B66:F66"/>
+    <mergeCell ref="A602:F602"/>
     <mergeCell ref="B326:F326"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="A533:F533"/>
+    <mergeCell ref="A604:F604"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A312:F312"/>
     <mergeCell ref="A483:F483"/>
